--- a/Assets/Game_Design/조작법 정리.xlsx
+++ b/Assets/Game_Design/조작법 정리.xlsx
@@ -129,7 +129,7 @@
     <t>벽·울타리 타기 가능</t>
   </si>
   <si>
-    <t>창문 침입, 하수구 진입, 옥상 접근</t>
+    <t>울타리 벽 넘기, 창문 넘기</t>
   </si>
   <si>
     <t>타기 중 S로 취소 가능</t>
@@ -248,50 +248,8 @@
       <patternFill patternType="lightGray"/>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="12">
     <border/>
-    <border>
-      <left style="thin">
-        <color rgb="FF284E3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF356854"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF284E3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF284E3F"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF356854"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF356854"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF284E3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF284E3F"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF356854"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF284E3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF284E3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF284E3F"/>
-      </bottom>
-    </border>
     <border>
       <left style="thin">
         <color rgb="FF284E3F"/>
@@ -380,6 +338,16 @@
       <left style="thin">
         <color rgb="FF284E3F"/>
       </left>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="FF284E3F"/>
+      </right>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF284E3F"/>
+      </left>
       <right style="thin">
         <color rgb="FFF6F8F9"/>
       </right>
@@ -422,35 +390,20 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="18">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="3" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="5" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="6" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="7" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="8" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="9" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="3" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -462,23 +415,29 @@
     <xf borderId="6" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="8" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf borderId="2" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="3" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="6" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="7" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="8" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
     <xf borderId="9" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="10" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
@@ -486,14 +445,11 @@
     <xf borderId="11" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="12" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="5">
     <dxf>
       <font/>
       <fill>
@@ -531,12 +487,29 @@
       </fill>
       <border/>
     </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color rgb="FF356854"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF356854"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF356854"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF356854"/>
+        </bottom>
+      </border>
+    </dxf>
   </dxfs>
   <tableStyles count="1">
-    <tableStyle count="3" pivot="0" name="조작법-style">
+    <tableStyle count="4" pivot="0" name="조작법-style">
       <tableStyleElement dxfId="1" type="headerRow"/>
       <tableStyleElement dxfId="2" type="firstRowStripe"/>
       <tableStyleElement dxfId="3" type="secondRowStripe"/>
+      <tableStyleElement dxfId="4" size="0" type="wholeTable"/>
     </tableStyle>
   </tableStyles>
 </styleSheet>
@@ -771,174 +744,174 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="4" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="E3" s="7" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="4" ht="15.75" customHeight="1">
-      <c r="A4" s="10" t="s">
+      <c r="A4" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="E4" s="10" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="E5" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" s="10" t="s">
+      <c r="A6" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="D6" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="E6" s="12" t="s">
+      <c r="E6" s="10" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="E7" s="9" t="s">
+      <c r="E7" s="7" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="B8" s="13" t="s">
+      <c r="B8" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="C8" s="13" t="s">
+      <c r="C8" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="E8" s="9" t="s">
+      <c r="E8" s="7" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="10" t="s">
+      <c r="A9" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="11" t="s">
+      <c r="B9" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="C9" s="11" t="s">
+      <c r="C9" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="D9" s="11" t="s">
+      <c r="D9" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="E9" s="12" t="s">
+      <c r="E9" s="10" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="14" t="s">
+      <c r="A10" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="B10" s="15" t="s">
+      <c r="B10" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="C10" s="15" t="s">
+      <c r="C10" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="D10" s="15" t="s">
+      <c r="D10" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="E10" s="16" t="s">
+      <c r="E10" s="14" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" s="17" t="s">
+      <c r="A11" s="12" t="s">
         <v>48</v>
       </c>
       <c r="B11" s="13" t="s">
@@ -950,41 +923,41 @@
       <c r="D11" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="E11" s="18" t="s">
+      <c r="E11" s="14" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="12" ht="15.75" customHeight="1">
-      <c r="A12" s="14" t="s">
+      <c r="A12" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="B12" s="15" t="s">
+      <c r="B12" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="C12" s="15" t="s">
+      <c r="C12" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="D12" s="15" t="s">
+      <c r="D12" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="E12" s="16" t="s">
+      <c r="E12" s="14" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="13" ht="15.75" customHeight="1">
-      <c r="A13" s="19" t="s">
+      <c r="A13" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="B13" s="20" t="s">
+      <c r="B13" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="C13" s="20" t="s">
+      <c r="C13" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="D13" s="20" t="s">
+      <c r="D13" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="E13" s="21" t="s">
+      <c r="E13" s="17" t="s">
         <v>59</v>
       </c>
     </row>
